--- a/backend/templates/excel/plantilla_2.xlsx
+++ b/backend/templates/excel/plantilla_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnologicodeantioquia-my.sharepoint.com/personal/paola_garcia44_correo_tdea_edu_co/Documents/Escritorio/Automatización geotecnica/automatizacion_geotecnica/backend/templates/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{D37D9AEB-57D8-4227-A05E-19663CFACB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{963675F7-37A9-4FA1-B5E0-470033251D8C}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{D37D9AEB-57D8-4227-A05E-19663CFACB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9590293-1D85-4073-B850-52291E100647}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5805" yWindow="3705" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P3" sheetId="50" r:id="rId1"/>
@@ -860,98 +860,98 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="17" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1387,177 +1387,177 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="43"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="54"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="55"/>
     </row>
     <row r="4" spans="1:19" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="45"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="47"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="58"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="49" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="50"/>
     </row>
     <row r="6" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="51" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="59">
+      <c r="B7" s="49"/>
+      <c r="C7" s="60">
         <v>46106</v>
       </c>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="56" t="s">
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="56"/>
+      <c r="G7" s="38"/>
       <c r="H7" s="11">
         <v>63.5</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="61" t="s">
+      <c r="J7" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="61"/>
-      <c r="L7" s="62" t="s">
+      <c r="K7" s="39"/>
+      <c r="L7" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="63"/>
-      <c r="N7" s="52" t="s">
+      <c r="M7" s="41"/>
+      <c r="N7" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="O7" s="53"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="48"/>
     </row>
     <row r="8" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="49" t="s">
+      <c r="B8" s="49"/>
+      <c r="C8" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="49"/>
+      <c r="D8" s="50"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="56" t="s">
+      <c r="F8" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="56"/>
+      <c r="G8" s="38"/>
       <c r="H8" s="11">
         <v>0.76</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="65"/>
-      <c r="N8" s="52" t="s">
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="43"/>
+      <c r="N8" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="O8" s="53"/>
-      <c r="P8" s="53"/>
-      <c r="Q8" s="54"/>
+      <c r="O8" s="47"/>
+      <c r="P8" s="47"/>
+      <c r="Q8" s="48"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
@@ -1613,7 +1613,7 @@
       </c>
     </row>
     <row r="10" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="35">
+      <c r="A10" s="62">
         <v>0.45</v>
       </c>
       <c r="B10" s="16">
@@ -1631,7 +1631,7 @@
         <f t="shared" ref="E10:E16" si="1">C10-D10</f>
         <v>6.75</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="35">
         <v>15</v>
       </c>
       <c r="G10" s="17">
@@ -1673,12 +1673,12 @@
         <f>L10</f>
         <v>33.233731366492307</v>
       </c>
-      <c r="Q10" s="50" t="s">
+      <c r="Q10" s="44" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="A11" s="62">
         <v>1.45</v>
       </c>
       <c r="B11" s="16">
@@ -1696,7 +1696,7 @@
         <f t="shared" si="1"/>
         <v>24.65</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="35">
         <v>20</v>
       </c>
       <c r="G11" s="17">
@@ -1731,17 +1731,17 @@
         <f>0.32*(K11*45/55+15)</f>
         <v>11.971890739401534</v>
       </c>
-      <c r="O11" s="57">
+      <c r="O11" s="51">
         <v>5</v>
       </c>
       <c r="P11" s="14">
         <f t="shared" ref="P11:P25" si="10">L11</f>
         <v>33.504269183343119</v>
       </c>
-      <c r="Q11" s="50"/>
+      <c r="Q11" s="44"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="36">
+      <c r="A12" s="63">
         <v>2.4500000000000002</v>
       </c>
       <c r="B12" s="3">
@@ -1759,7 +1759,7 @@
         <f t="shared" si="1"/>
         <v>41.650000000000006</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="35">
         <v>22</v>
       </c>
       <c r="G12" s="2">
@@ -1794,15 +1794,15 @@
         <f t="shared" ref="N12:N16" si="12">0.32*(K12*45/55+15)</f>
         <v>11.74779291479981</v>
       </c>
-      <c r="O12" s="57"/>
+      <c r="O12" s="51"/>
       <c r="P12" s="14">
         <f t="shared" si="10"/>
         <v>33.212876300018692</v>
       </c>
-      <c r="Q12" s="50"/>
+      <c r="Q12" s="44"/>
     </row>
     <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="37">
+      <c r="A13" s="64">
         <v>3.45</v>
       </c>
       <c r="B13" s="24">
@@ -1820,7 +1820,7 @@
         <f t="shared" si="1"/>
         <v>58.650000000000006</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="35">
         <v>29</v>
       </c>
       <c r="G13" s="23">
@@ -1855,17 +1855,17 @@
         <f t="shared" si="12"/>
         <v>13.148760192223349</v>
       </c>
-      <c r="O13" s="57"/>
+      <c r="O13" s="51"/>
       <c r="P13" s="14">
         <f>L13</f>
         <v>34.964852157662726</v>
       </c>
-      <c r="Q13" s="50" t="s">
+      <c r="Q13" s="44" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="36">
+      <c r="A14" s="63">
         <v>4.45</v>
       </c>
       <c r="B14" s="3">
@@ -1883,7 +1883,7 @@
         <f t="shared" si="1"/>
         <v>75.650000000000006</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="35">
         <v>35</v>
       </c>
       <c r="G14" s="2">
@@ -1918,18 +1918,18 @@
         <f t="shared" si="12"/>
         <v>14.149414630341481</v>
       </c>
-      <c r="O14" s="57"/>
+      <c r="O14" s="51"/>
       <c r="P14" s="14">
         <f t="shared" si="10"/>
         <v>36.127461326631675</v>
       </c>
-      <c r="Q14" s="50"/>
+      <c r="Q14" s="44"/>
       <c r="S14">
         <v>0.217</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="35">
+      <c r="A15" s="62">
         <v>5.45</v>
       </c>
       <c r="B15" s="16">
@@ -1947,7 +1947,7 @@
         <f t="shared" si="1"/>
         <v>92.65</v>
       </c>
-      <c r="F15" s="39">
+      <c r="F15" s="35">
         <v>38</v>
       </c>
       <c r="G15" s="17">
@@ -1982,15 +1982,15 @@
         <f t="shared" si="12"/>
         <v>14.322451748193826</v>
       </c>
-      <c r="O15" s="57"/>
+      <c r="O15" s="51"/>
       <c r="P15" s="14">
         <f t="shared" si="10"/>
         <v>36.32207641950275</v>
       </c>
-      <c r="Q15" s="50"/>
+      <c r="Q15" s="44"/>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="38">
+      <c r="A16" s="65">
         <v>6.45</v>
       </c>
       <c r="B16" s="28">
@@ -2008,7 +2008,7 @@
         <f t="shared" si="1"/>
         <v>109.65</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="35">
         <v>42</v>
       </c>
       <c r="G16" s="27">
@@ -2043,15 +2043,15 @@
         <f t="shared" si="12"/>
         <v>14.747661600533407</v>
       </c>
-      <c r="O16" s="57"/>
+      <c r="O16" s="51"/>
       <c r="P16" s="14">
         <f t="shared" si="10"/>
         <v>36.792929138648006</v>
       </c>
-      <c r="Q16" s="50"/>
+      <c r="Q16" s="44"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="37">
+      <c r="A17" s="64">
         <v>7.45</v>
       </c>
       <c r="B17" s="24">
@@ -2069,7 +2069,7 @@
         <f t="shared" ref="E17:E25" si="15">C17-D17</f>
         <v>127.65</v>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="35">
         <v>45</v>
       </c>
       <c r="G17" s="23">
@@ -2109,10 +2109,10 @@
         <f t="shared" si="10"/>
         <v>36.959458019013667</v>
       </c>
-      <c r="Q17" s="50"/>
+      <c r="Q17" s="44"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="36">
+      <c r="A18" s="63">
         <v>8.4499999999999993</v>
       </c>
       <c r="B18" s="3">
@@ -2130,7 +2130,7 @@
         <f t="shared" si="15"/>
         <v>145.64999999999998</v>
       </c>
-      <c r="F18" s="39">
+      <c r="F18" s="35">
         <v>48</v>
       </c>
       <c r="G18" s="2">
@@ -2170,10 +2170,10 @@
         <f t="shared" si="10"/>
         <v>37.129314496641506</v>
       </c>
-      <c r="Q18" s="50"/>
+      <c r="Q18" s="44"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="36">
+      <c r="A19" s="63">
         <v>9.4499999999999993</v>
       </c>
       <c r="B19" s="3">
@@ -2191,7 +2191,7 @@
         <f t="shared" si="15"/>
         <v>163.64999999999998</v>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="35">
         <v>51</v>
       </c>
       <c r="G19" s="2">
@@ -2231,10 +2231,10 @@
         <f t="shared" si="10"/>
         <v>37.297304751651886</v>
       </c>
-      <c r="Q19" s="50"/>
+      <c r="Q19" s="44"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="36">
+      <c r="A20" s="63">
         <v>10.45</v>
       </c>
       <c r="B20" s="3">
@@ -2252,7 +2252,7 @@
         <f t="shared" si="15"/>
         <v>181.64999999999998</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="36">
         <v>54</v>
       </c>
       <c r="G20" s="2">
@@ -2292,10 +2292,10 @@
         <f t="shared" si="10"/>
         <v>37.460409475972369</v>
       </c>
-      <c r="Q20" s="50"/>
+      <c r="Q20" s="44"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="36">
+      <c r="A21" s="63">
         <v>11.45</v>
       </c>
       <c r="B21" s="3">
@@ -2313,7 +2313,7 @@
         <f t="shared" si="15"/>
         <v>199.64999999999998</v>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="36">
         <v>57</v>
       </c>
       <c r="G21" s="2">
@@ -2353,10 +2353,10 @@
         <f t="shared" si="10"/>
         <v>37.616858708716265</v>
       </c>
-      <c r="Q21" s="50"/>
+      <c r="Q21" s="44"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="36">
+      <c r="A22" s="63">
         <v>12.45</v>
       </c>
       <c r="B22" s="3">
@@ -2374,7 +2374,7 @@
         <f t="shared" si="15"/>
         <v>217.64999999999998</v>
       </c>
-      <c r="F22" s="40">
+      <c r="F22" s="36">
         <v>59</v>
       </c>
       <c r="G22" s="2">
@@ -2414,10 +2414,10 @@
         <f t="shared" si="10"/>
         <v>37.575119704426996</v>
       </c>
-      <c r="Q22" s="50"/>
+      <c r="Q22" s="44"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="36">
+      <c r="A23" s="63">
         <v>13.45</v>
       </c>
       <c r="B23" s="3">
@@ -2435,7 +2435,7 @@
         <f t="shared" si="15"/>
         <v>235.64999999999998</v>
       </c>
-      <c r="F23" s="40">
+      <c r="F23" s="36">
         <v>62</v>
       </c>
       <c r="G23" s="2">
@@ -2475,10 +2475,10 @@
         <f t="shared" si="10"/>
         <v>37.723641699800552</v>
       </c>
-      <c r="Q23" s="50"/>
+      <c r="Q23" s="44"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="36">
+      <c r="A24" s="63">
         <v>14.45</v>
       </c>
       <c r="B24" s="3">
@@ -2496,7 +2496,7 @@
         <f t="shared" si="15"/>
         <v>253.64999999999998</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="36">
         <v>65</v>
       </c>
       <c r="G24" s="2">
@@ -2536,10 +2536,10 @@
         <f t="shared" si="10"/>
         <v>37.862990650569699</v>
       </c>
-      <c r="Q24" s="50"/>
+      <c r="Q24" s="44"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="36">
+      <c r="A25" s="63">
         <v>15.45</v>
       </c>
       <c r="B25" s="3">
@@ -2557,7 +2557,7 @@
         <f t="shared" si="15"/>
         <v>271.64999999999998</v>
       </c>
-      <c r="F25" s="40">
+      <c r="F25" s="36">
         <v>68</v>
       </c>
       <c r="G25" s="2">
@@ -2597,16 +2597,16 @@
         <f t="shared" si="10"/>
         <v>37.993168713005147</v>
       </c>
-      <c r="Q25" s="50"/>
+      <c r="Q25" s="44"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="20"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="58" t="s">
+      <c r="A27" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="58"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="29" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="21"/>
@@ -2631,11 +2631,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J7:K8"/>
-    <mergeCell ref="L7:M8"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:Q5"/>
     <mergeCell ref="Q10:Q12"/>
     <mergeCell ref="Q13:Q25"/>
     <mergeCell ref="A6:B6"/>
@@ -2647,11 +2647,11 @@
     <mergeCell ref="N8:Q8"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="O11:O16"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A3:Q3"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:Q5"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J7:K8"/>
+    <mergeCell ref="L7:M8"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.55118110236220474" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/backend/templates/excel/plantilla_2.xlsx
+++ b/backend/templates/excel/plantilla_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnologicodeantioquia-my.sharepoint.com/personal/paola_garcia44_correo_tdea_edu_co/Documents/Escritorio/Automatización geotecnica/automatizacion_geotecnica/backend/templates/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{D37D9AEB-57D8-4227-A05E-19663CFACB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9590293-1D85-4073-B850-52291E100647}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{D37D9AEB-57D8-4227-A05E-19663CFACB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B820EDD-27B7-4A9D-BCFF-14A163B70304}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5805" yWindow="3705" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P3" sheetId="50" r:id="rId1"/>
@@ -860,16 +860,76 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -887,71 +947,11 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1387,177 +1387,177 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="54"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="41"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="55"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
     </row>
     <row r="4" spans="1:19" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
-      <c r="P4" s="57"/>
-      <c r="Q4" s="58"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="45"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="50" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="47"/>
     </row>
     <row r="6" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="59" t="s">
+      <c r="B6" s="46"/>
+      <c r="C6" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="59"/>
-      <c r="Q6" s="59"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="60">
+      <c r="B7" s="53"/>
+      <c r="C7" s="57">
         <v>46106</v>
       </c>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="38" t="s">
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="38"/>
+      <c r="G7" s="54"/>
       <c r="H7" s="11">
         <v>63.5</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="39" t="s">
+      <c r="J7" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="39"/>
-      <c r="L7" s="40" t="s">
+      <c r="K7" s="59"/>
+      <c r="L7" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="41"/>
-      <c r="N7" s="46" t="s">
+      <c r="M7" s="61"/>
+      <c r="N7" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="48"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="52"/>
     </row>
     <row r="8" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50" t="s">
+      <c r="B8" s="53"/>
+      <c r="C8" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="50"/>
+      <c r="D8" s="47"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="38"/>
+      <c r="G8" s="54"/>
       <c r="H8" s="11">
         <v>0.76</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="46" t="s">
+      <c r="J8" s="59"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="O8" s="47"/>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="48"/>
+      <c r="O8" s="51"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="52"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
@@ -1613,7 +1613,7 @@
       </c>
     </row>
     <row r="10" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="62">
+      <c r="A10" s="35">
         <v>0.45</v>
       </c>
       <c r="B10" s="16">
@@ -1631,7 +1631,7 @@
         <f t="shared" ref="E10:E16" si="1">C10-D10</f>
         <v>6.75</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="64">
         <v>15</v>
       </c>
       <c r="G10" s="17">
@@ -1673,12 +1673,12 @@
         <f>L10</f>
         <v>33.233731366492307</v>
       </c>
-      <c r="Q10" s="44" t="s">
+      <c r="Q10" s="48" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="62">
+      <c r="A11" s="35">
         <v>1.45</v>
       </c>
       <c r="B11" s="16">
@@ -1696,7 +1696,7 @@
         <f t="shared" si="1"/>
         <v>24.65</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="64">
         <v>20</v>
       </c>
       <c r="G11" s="17">
@@ -1731,17 +1731,17 @@
         <f>0.32*(K11*45/55+15)</f>
         <v>11.971890739401534</v>
       </c>
-      <c r="O11" s="51">
+      <c r="O11" s="55">
         <v>5</v>
       </c>
       <c r="P11" s="14">
         <f t="shared" ref="P11:P25" si="10">L11</f>
         <v>33.504269183343119</v>
       </c>
-      <c r="Q11" s="44"/>
+      <c r="Q11" s="48"/>
     </row>
     <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="63">
+      <c r="A12" s="36">
         <v>2.4500000000000002</v>
       </c>
       <c r="B12" s="3">
@@ -1759,7 +1759,7 @@
         <f t="shared" si="1"/>
         <v>41.650000000000006</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="64">
         <v>22</v>
       </c>
       <c r="G12" s="2">
@@ -1794,15 +1794,15 @@
         <f t="shared" ref="N12:N16" si="12">0.32*(K12*45/55+15)</f>
         <v>11.74779291479981</v>
       </c>
-      <c r="O12" s="51"/>
+      <c r="O12" s="55"/>
       <c r="P12" s="14">
         <f t="shared" si="10"/>
         <v>33.212876300018692</v>
       </c>
-      <c r="Q12" s="44"/>
+      <c r="Q12" s="48"/>
     </row>
     <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="64">
+      <c r="A13" s="37">
         <v>3.45</v>
       </c>
       <c r="B13" s="24">
@@ -1820,7 +1820,7 @@
         <f t="shared" si="1"/>
         <v>58.650000000000006</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="64">
         <v>29</v>
       </c>
       <c r="G13" s="23">
@@ -1855,17 +1855,17 @@
         <f t="shared" si="12"/>
         <v>13.148760192223349</v>
       </c>
-      <c r="O13" s="51"/>
+      <c r="O13" s="55"/>
       <c r="P13" s="14">
         <f>L13</f>
         <v>34.964852157662726</v>
       </c>
-      <c r="Q13" s="44" t="s">
+      <c r="Q13" s="48" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="63">
+      <c r="A14" s="36">
         <v>4.45</v>
       </c>
       <c r="B14" s="3">
@@ -1883,7 +1883,7 @@
         <f t="shared" si="1"/>
         <v>75.650000000000006</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="64">
         <v>35</v>
       </c>
       <c r="G14" s="2">
@@ -1918,18 +1918,18 @@
         <f t="shared" si="12"/>
         <v>14.149414630341481</v>
       </c>
-      <c r="O14" s="51"/>
+      <c r="O14" s="55"/>
       <c r="P14" s="14">
         <f t="shared" si="10"/>
         <v>36.127461326631675</v>
       </c>
-      <c r="Q14" s="44"/>
+      <c r="Q14" s="48"/>
       <c r="S14">
         <v>0.217</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="62">
+      <c r="A15" s="35">
         <v>5.45</v>
       </c>
       <c r="B15" s="16">
@@ -1947,7 +1947,7 @@
         <f t="shared" si="1"/>
         <v>92.65</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="64">
         <v>38</v>
       </c>
       <c r="G15" s="17">
@@ -1982,15 +1982,15 @@
         <f t="shared" si="12"/>
         <v>14.322451748193826</v>
       </c>
-      <c r="O15" s="51"/>
+      <c r="O15" s="55"/>
       <c r="P15" s="14">
         <f t="shared" si="10"/>
         <v>36.32207641950275</v>
       </c>
-      <c r="Q15" s="44"/>
+      <c r="Q15" s="48"/>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="65">
+      <c r="A16" s="38">
         <v>6.45</v>
       </c>
       <c r="B16" s="28">
@@ -2008,7 +2008,7 @@
         <f t="shared" si="1"/>
         <v>109.65</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="64">
         <v>42</v>
       </c>
       <c r="G16" s="27">
@@ -2043,15 +2043,15 @@
         <f t="shared" si="12"/>
         <v>14.747661600533407</v>
       </c>
-      <c r="O16" s="51"/>
+      <c r="O16" s="55"/>
       <c r="P16" s="14">
         <f t="shared" si="10"/>
         <v>36.792929138648006</v>
       </c>
-      <c r="Q16" s="44"/>
+      <c r="Q16" s="48"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="64">
+      <c r="A17" s="37">
         <v>7.45</v>
       </c>
       <c r="B17" s="24">
@@ -2069,7 +2069,7 @@
         <f t="shared" ref="E17:E25" si="15">C17-D17</f>
         <v>127.65</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="64">
         <v>45</v>
       </c>
       <c r="G17" s="23">
@@ -2109,10 +2109,10 @@
         <f t="shared" si="10"/>
         <v>36.959458019013667</v>
       </c>
-      <c r="Q17" s="44"/>
+      <c r="Q17" s="48"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="63">
+      <c r="A18" s="36">
         <v>8.4499999999999993</v>
       </c>
       <c r="B18" s="3">
@@ -2130,7 +2130,7 @@
         <f t="shared" si="15"/>
         <v>145.64999999999998</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="64">
         <v>48</v>
       </c>
       <c r="G18" s="2">
@@ -2170,10 +2170,10 @@
         <f t="shared" si="10"/>
         <v>37.129314496641506</v>
       </c>
-      <c r="Q18" s="44"/>
+      <c r="Q18" s="48"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="63">
+      <c r="A19" s="36">
         <v>9.4499999999999993</v>
       </c>
       <c r="B19" s="3">
@@ -2191,7 +2191,7 @@
         <f t="shared" si="15"/>
         <v>163.64999999999998</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="64">
         <v>51</v>
       </c>
       <c r="G19" s="2">
@@ -2231,10 +2231,10 @@
         <f t="shared" si="10"/>
         <v>37.297304751651886</v>
       </c>
-      <c r="Q19" s="44"/>
+      <c r="Q19" s="48"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="63">
+      <c r="A20" s="36">
         <v>10.45</v>
       </c>
       <c r="B20" s="3">
@@ -2252,7 +2252,7 @@
         <f t="shared" si="15"/>
         <v>181.64999999999998</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="65">
         <v>54</v>
       </c>
       <c r="G20" s="2">
@@ -2292,10 +2292,10 @@
         <f t="shared" si="10"/>
         <v>37.460409475972369</v>
       </c>
-      <c r="Q20" s="44"/>
+      <c r="Q20" s="48"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="63">
+      <c r="A21" s="36">
         <v>11.45</v>
       </c>
       <c r="B21" s="3">
@@ -2313,7 +2313,7 @@
         <f t="shared" si="15"/>
         <v>199.64999999999998</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="65">
         <v>57</v>
       </c>
       <c r="G21" s="2">
@@ -2353,10 +2353,10 @@
         <f t="shared" si="10"/>
         <v>37.616858708716265</v>
       </c>
-      <c r="Q21" s="44"/>
+      <c r="Q21" s="48"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="63">
+      <c r="A22" s="36">
         <v>12.45</v>
       </c>
       <c r="B22" s="3">
@@ -2374,7 +2374,7 @@
         <f t="shared" si="15"/>
         <v>217.64999999999998</v>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="65">
         <v>59</v>
       </c>
       <c r="G22" s="2">
@@ -2414,10 +2414,10 @@
         <f t="shared" si="10"/>
         <v>37.575119704426996</v>
       </c>
-      <c r="Q22" s="44"/>
+      <c r="Q22" s="48"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="63">
+      <c r="A23" s="36">
         <v>13.45</v>
       </c>
       <c r="B23" s="3">
@@ -2435,7 +2435,7 @@
         <f t="shared" si="15"/>
         <v>235.64999999999998</v>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="65">
         <v>62</v>
       </c>
       <c r="G23" s="2">
@@ -2475,10 +2475,10 @@
         <f t="shared" si="10"/>
         <v>37.723641699800552</v>
       </c>
-      <c r="Q23" s="44"/>
+      <c r="Q23" s="48"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="63">
+      <c r="A24" s="36">
         <v>14.45</v>
       </c>
       <c r="B24" s="3">
@@ -2496,7 +2496,7 @@
         <f t="shared" si="15"/>
         <v>253.64999999999998</v>
       </c>
-      <c r="F24" s="36">
+      <c r="F24" s="65">
         <v>65</v>
       </c>
       <c r="G24" s="2">
@@ -2536,10 +2536,10 @@
         <f t="shared" si="10"/>
         <v>37.862990650569699</v>
       </c>
-      <c r="Q24" s="44"/>
+      <c r="Q24" s="48"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="63">
+      <c r="A25" s="36">
         <v>15.45</v>
       </c>
       <c r="B25" s="3">
@@ -2557,7 +2557,7 @@
         <f t="shared" si="15"/>
         <v>271.64999999999998</v>
       </c>
-      <c r="F25" s="36">
+      <c r="F25" s="65">
         <v>68</v>
       </c>
       <c r="G25" s="2">
@@ -2597,16 +2597,16 @@
         <f t="shared" si="10"/>
         <v>37.993168713005147</v>
       </c>
-      <c r="Q25" s="44"/>
+      <c r="Q25" s="48"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="20"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="37"/>
+      <c r="B27" s="56"/>
     </row>
     <row r="29" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="21"/>
@@ -2631,11 +2631,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A3:Q3"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:Q5"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J7:K8"/>
+    <mergeCell ref="L7:M8"/>
     <mergeCell ref="Q10:Q12"/>
     <mergeCell ref="Q13:Q25"/>
     <mergeCell ref="A6:B6"/>
@@ -2647,11 +2647,11 @@
     <mergeCell ref="N8:Q8"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="O11:O16"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J7:K8"/>
-    <mergeCell ref="L7:M8"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:Q5"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.55118110236220474" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
